--- a/Result/profitability/6023.xlsx
+++ b/Result/profitability/6023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,10 +663,10 @@
         <v>1.16</v>
       </c>
       <c r="M2" t="n">
-        <v>1.99125</v>
+        <v>2.00875</v>
       </c>
       <c r="N2" t="n">
-        <v>35.98625</v>
+        <v>36.79375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -768,10 +768,10 @@
         <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8425</v>
+        <v>1.88625</v>
       </c>
       <c r="N3" t="n">
-        <v>39.51625</v>
+        <v>41.19625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -881,10 +881,10 @@
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.76125</v>
+        <v>1.7875</v>
       </c>
       <c r="N4" t="n">
-        <v>44.42375</v>
+        <v>45.3625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -994,10 +994,10 @@
         <v>1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>1.69</v>
+        <v>1.70875</v>
       </c>
       <c r="N5" t="n">
-        <v>48.9525</v>
+        <v>49.7875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1107,10 +1107,10 @@
         <v>1.07</v>
       </c>
       <c r="M6" t="n">
-        <v>1.55625</v>
+        <v>1.56625</v>
       </c>
       <c r="N6" t="n">
-        <v>52.64</v>
+        <v>53.73</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1228,10 +1228,10 @@
         <v>0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>1.37625</v>
+        <v>1.405</v>
       </c>
       <c r="N7" t="n">
-        <v>55.85</v>
+        <v>56.45125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1349,10 +1349,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>1.16125</v>
+        <v>1.17375</v>
       </c>
       <c r="N8" t="n">
-        <v>57.975</v>
+        <v>58.29625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1836,7 +1836,7 @@
         <v>0.68875</v>
       </c>
       <c r="N12" t="n">
-        <v>56.6325</v>
+        <v>56.63249999999999</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9388,6 +9388,127 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1276</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>39.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-204</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-16.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="n">
+        <v>1094</v>
+      </c>
+      <c r="K75" t="n">
+        <v>843</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.1325</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.89625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.04566210045662111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.07021857923497277</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.1499999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.07009345794392519</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2056017236072638</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
